--- a/sample/work/sample1.xlsx
+++ b/sample/work/sample1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\p\ExcelToCSV\sample\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F5FE05-EF0D-45CA-9BA3-725316086EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44870FD7-212B-4047-BE4F-C7A381E98CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A501FB7A-F3F0-4D58-BC7E-EC7EFCD39EDB}"/>
   </bookViews>

--- a/sample/work/sample1.xlsx
+++ b/sample/work/sample1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\p\ExcelToCSV\sample\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44870FD7-212B-4047-BE4F-C7A381E98CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3041B1E4-4F82-46D8-BF7E-E4AFF40A5D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A501FB7A-F3F0-4D58-BC7E-EC7EFCD39EDB}"/>
   </bookViews>
